--- a/costos.xlsx
+++ b/costos.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uanledu-my.sharepoint.com/personal/grecia_hernandezgnz_uanl_edu_mx/Documents/7mo/Computo Integrado/Omnihub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\omnihub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="11_F25DC773A252ABDACC10489409DB71645BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C30CF57-7AF6-4E1C-9CB9-CE92DDFB1B82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5F57D1-D522-41F7-B7C2-19A605912A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="actual" sheetId="1" r:id="rId1"/>
     <sheet name="colchon" sheetId="3" r:id="rId2"/>
+    <sheet name="final" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
   <si>
     <t>material</t>
   </si>
@@ -142,6 +143,66 @@
   </si>
   <si>
     <t>sum</t>
+  </si>
+  <si>
+    <t>pagos</t>
+  </si>
+  <si>
+    <t>fechas</t>
+  </si>
+  <si>
+    <t>concepto</t>
+  </si>
+  <si>
+    <t>monto</t>
+  </si>
+  <si>
+    <t>bruno</t>
+  </si>
+  <si>
+    <t>bryan</t>
+  </si>
+  <si>
+    <t>josue</t>
+  </si>
+  <si>
+    <t>monse</t>
+  </si>
+  <si>
+    <t>raspi</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>ORD</t>
+  </si>
+  <si>
+    <t>ORD-caja</t>
+  </si>
+  <si>
+    <t>para despues de mc</t>
+  </si>
+  <si>
+    <t>caja</t>
+  </si>
+  <si>
+    <t>transistor+rele</t>
+  </si>
+  <si>
+    <t>gastado(REAL)</t>
+  </si>
+  <si>
+    <t>mc switchers</t>
+  </si>
+  <si>
+    <t>ord switchers</t>
+  </si>
+  <si>
+    <t>deben</t>
   </si>
 </sst>
 </file>
@@ -216,22 +277,22 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -300,7 +361,7 @@
     <tableColumn id="9" xr3:uid="{1664EE51-5650-4620-8CF5-8D8EEAF38028}" name="amazon"/>
     <tableColumn id="4" xr3:uid="{FDB68956-16DD-4C6B-ACAE-CCB928851AC5}" name="donchip"/>
     <tableColumn id="5" xr3:uid="{2750BB18-1DC4-4977-91CB-610D7A3CFE34}" name="cantidad"/>
-    <tableColumn id="6" xr3:uid="{13C03178-7C1F-4A3A-ADF5-D13C5F72A2D2}" name="total" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="6" xr3:uid="{13C03178-7C1F-4A3A-ADF5-D13C5F72A2D2}" name="total" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>Table2[[#This Row],[precio]]*Table2[[#This Row],[cantidad]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -571,27 +632,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:L12"/>
+  <dimension ref="C3:K23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="E4" s="7" t="s">
+    <row r="4" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
         <v>0</v>
       </c>
@@ -604,10 +665,9 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
         <v>3</v>
       </c>
@@ -621,14 +681,14 @@
         <f>G6*F6</f>
         <v>100</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="K6">
         <v>2808</v>
       </c>
     </row>
-    <row r="7" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E7" t="s">
         <v>4</v>
       </c>
@@ -642,12 +702,12 @@
         <f t="shared" ref="H7:H11" si="0">G7*F7</f>
         <v>10</v>
       </c>
-      <c r="J7" s="10"/>
+      <c r="J7" s="7"/>
       <c r="K7">
         <v>414</v>
       </c>
     </row>
-    <row r="8" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E8" t="s">
         <v>5</v>
       </c>
@@ -669,7 +729,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="9" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
         <v>6</v>
       </c>
@@ -686,12 +746,12 @@
       <c r="J9" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <f>K8-H12</f>
         <v>1935</v>
       </c>
     </row>
-    <row r="10" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E10" t="s">
         <v>7</v>
       </c>
@@ -706,7 +766,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
         <v>8</v>
       </c>
@@ -721,10 +781,69 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:11" x14ac:dyDescent="0.35">
       <c r="H12">
         <f>SUM(H6:H11)</f>
         <v>1287</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <f>60+99</f>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21">
+        <f>1060+189</f>
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <f>SUM(F18:F22)</f>
+        <v>3210</v>
       </c>
     </row>
   </sheetData>
@@ -751,49 +870,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4">
+      <c r="D4" s="2"/>
+      <c r="E4" s="3">
         <v>5</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4">
@@ -805,15 +924,15 @@
       </c>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4">
+      <c r="D5" s="2"/>
+      <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H5">
@@ -854,7 +973,7 @@
         <f>M11+N11</f>
         <v>2808.75</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <f>M6/4</f>
         <v>702.1875</v>
       </c>
@@ -863,7 +982,7 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E7">
@@ -884,7 +1003,7 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E8">
@@ -905,7 +1024,7 @@
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E9">
@@ -926,7 +1045,7 @@
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E10">
@@ -957,7 +1076,7 @@
         <f>SUM(I4:I10)</f>
         <v>2247</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <f>M11/4</f>
         <v>561.75</v>
       </c>
@@ -981,4 +1100,205 @@
     <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1DE1B7-05EF-430B-88F6-9EEC34B63000}">
+  <dimension ref="E9:M18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>45535</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>330</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>45553</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11">
+        <v>702</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" s="10">
+        <v>45567</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>103</v>
+      </c>
+      <c r="J12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13" s="10">
+        <v>45590</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13">
+        <v>312</v>
+      </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" s="10">
+        <v>45615</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
+        <v>50</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15">
+        <f>SUM(H10:H14)</f>
+        <v>1497</v>
+      </c>
+      <c r="I15" s="5">
+        <f>H15-(H10+H11)</f>
+        <v>465</v>
+      </c>
+      <c r="J15" s="5">
+        <v>50</v>
+      </c>
+      <c r="K15" s="5">
+        <f>SUM(H12,H14)</f>
+        <v>153</v>
+      </c>
+      <c r="L15" s="5">
+        <v>50</v>
+      </c>
+      <c r="M15">
+        <f>SUM(I15:L15)</f>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <f>H15*4</f>
+        <v>5988</v>
+      </c>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="18" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="5">
+        <f>H16-H17</f>
+        <v>2778</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>